--- a/figures/lecture5/6345.0/634504b.xlsx
+++ b/figures/lecture5/6345.0/634504b.xlsx
@@ -17,89 +17,89 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A2599999R">Data1!$B$1:$B$10,Data1!$B$11:$B$114</definedName>
-    <definedName name="A2599999R_Data">Data1!$B$11:$B$114</definedName>
-    <definedName name="A2599999R_Latest">Data1!$B$114</definedName>
-    <definedName name="A2600000C">Data1!$K$1:$K$10,Data1!$K$11:$K$114</definedName>
-    <definedName name="A2600000C_Data">Data1!$K$11:$K$114</definedName>
-    <definedName name="A2600000C_Latest">Data1!$K$114</definedName>
-    <definedName name="A2600001F">Data1!$T$1:$T$10,Data1!$T$11:$T$114</definedName>
-    <definedName name="A2600001F_Data">Data1!$T$11:$T$114</definedName>
-    <definedName name="A2600001F_Latest">Data1!$T$114</definedName>
-    <definedName name="A2601329C">Data1!$D$1:$D$10,Data1!$D$11:$D$114</definedName>
-    <definedName name="A2601329C_Data">Data1!$D$11:$D$114</definedName>
-    <definedName name="A2601329C_Latest">Data1!$D$114</definedName>
-    <definedName name="A2601330L">Data1!$M$1:$M$10,Data1!$M$11:$M$114</definedName>
-    <definedName name="A2601330L_Data">Data1!$M$11:$M$114</definedName>
-    <definedName name="A2601330L_Latest">Data1!$M$114</definedName>
-    <definedName name="A2601331R">Data1!$V$1:$V$10,Data1!$V$11:$V$114</definedName>
-    <definedName name="A2601331R_Data">Data1!$V$11:$V$114</definedName>
-    <definedName name="A2601331R_Latest">Data1!$V$114</definedName>
-    <definedName name="A2602659L">Data1!$G$1:$G$10,Data1!$G$11:$G$114</definedName>
-    <definedName name="A2602659L_Data">Data1!$G$11:$G$114</definedName>
-    <definedName name="A2602659L_Latest">Data1!$G$114</definedName>
-    <definedName name="A2602660W">Data1!$P$1:$P$10,Data1!$P$11:$P$114</definedName>
-    <definedName name="A2602660W_Data">Data1!$P$11:$P$114</definedName>
-    <definedName name="A2602660W_Latest">Data1!$P$114</definedName>
-    <definedName name="A2602661X">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$114</definedName>
-    <definedName name="A2602661X_Data">Data1!$Y$11:$Y$114</definedName>
-    <definedName name="A2602661X_Latest">Data1!$Y$114</definedName>
-    <definedName name="A2603989W">Data1!$J$1:$J$10,Data1!$J$11:$J$114</definedName>
-    <definedName name="A2603989W_Data">Data1!$J$11:$J$114</definedName>
-    <definedName name="A2603989W_Latest">Data1!$J$114</definedName>
-    <definedName name="A2603990F">Data1!$S$1:$S$10,Data1!$S$11:$S$114</definedName>
-    <definedName name="A2603990F_Data">Data1!$S$11:$S$114</definedName>
-    <definedName name="A2603990F_Latest">Data1!$S$114</definedName>
-    <definedName name="A2603991J">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$114</definedName>
-    <definedName name="A2603991J_Data">Data1!$AB$11:$AB$114</definedName>
-    <definedName name="A2603991J_Latest">Data1!$AB$114</definedName>
-    <definedName name="A2605319W">Data1!$I$1:$I$10,Data1!$I$11:$I$114</definedName>
-    <definedName name="A2605319W_Data">Data1!$I$11:$I$114</definedName>
-    <definedName name="A2605319W_Latest">Data1!$I$114</definedName>
-    <definedName name="A2605320F">Data1!$R$1:$R$10,Data1!$R$11:$R$114</definedName>
-    <definedName name="A2605320F_Data">Data1!$R$11:$R$114</definedName>
-    <definedName name="A2605320F_Latest">Data1!$R$114</definedName>
-    <definedName name="A2605321J">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$114</definedName>
-    <definedName name="A2605321J_Data">Data1!$AA$11:$AA$114</definedName>
-    <definedName name="A2605321J_Latest">Data1!$AA$114</definedName>
-    <definedName name="A2606649F">Data1!$H$1:$H$10,Data1!$H$11:$H$114</definedName>
-    <definedName name="A2606649F_Data">Data1!$H$11:$H$114</definedName>
-    <definedName name="A2606649F_Latest">Data1!$H$114</definedName>
-    <definedName name="A2606650R">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$114</definedName>
-    <definedName name="A2606650R_Data">Data1!$Q$11:$Q$114</definedName>
-    <definedName name="A2606650R_Latest">Data1!$Q$114</definedName>
-    <definedName name="A2606651T">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$114</definedName>
-    <definedName name="A2606651T_Data">Data1!$Z$11:$Z$114</definedName>
-    <definedName name="A2606651T_Latest">Data1!$Z$114</definedName>
-    <definedName name="A2607979R">Data1!$F$1:$F$10,Data1!$F$11:$F$114</definedName>
-    <definedName name="A2607979R_Data">Data1!$F$11:$F$114</definedName>
-    <definedName name="A2607979R_Latest">Data1!$F$114</definedName>
-    <definedName name="A2607980X">Data1!$O$1:$O$10,Data1!$O$11:$O$114</definedName>
-    <definedName name="A2607980X_Data">Data1!$O$11:$O$114</definedName>
-    <definedName name="A2607980X_Latest">Data1!$O$114</definedName>
-    <definedName name="A2607981A">Data1!$X$1:$X$10,Data1!$X$11:$X$114</definedName>
-    <definedName name="A2607981A_Data">Data1!$X$11:$X$114</definedName>
-    <definedName name="A2607981A_Latest">Data1!$X$114</definedName>
-    <definedName name="A2609309R">Data1!$C$1:$C$10,Data1!$C$11:$C$114</definedName>
-    <definedName name="A2609309R_Data">Data1!$C$11:$C$114</definedName>
-    <definedName name="A2609309R_Latest">Data1!$C$114</definedName>
-    <definedName name="A2609310X">Data1!$L$1:$L$10,Data1!$L$11:$L$114</definedName>
-    <definedName name="A2609310X_Data">Data1!$L$11:$L$114</definedName>
-    <definedName name="A2609310X_Latest">Data1!$L$114</definedName>
-    <definedName name="A2609311A">Data1!$U$1:$U$10,Data1!$U$11:$U$114</definedName>
-    <definedName name="A2609311A_Data">Data1!$U$11:$U$114</definedName>
-    <definedName name="A2609311A_Latest">Data1!$U$114</definedName>
-    <definedName name="A2610639C">Data1!$E$1:$E$10,Data1!$E$11:$E$114</definedName>
-    <definedName name="A2610639C_Data">Data1!$E$11:$E$114</definedName>
-    <definedName name="A2610639C_Latest">Data1!$E$114</definedName>
-    <definedName name="A2610640L">Data1!$N$1:$N$10,Data1!$N$11:$N$114</definedName>
-    <definedName name="A2610640L_Data">Data1!$N$11:$N$114</definedName>
-    <definedName name="A2610640L_Latest">Data1!$N$114</definedName>
-    <definedName name="A2610641R">Data1!$W$1:$W$10,Data1!$W$11:$W$114</definedName>
-    <definedName name="A2610641R_Data">Data1!$W$11:$W$114</definedName>
-    <definedName name="A2610641R_Latest">Data1!$W$114</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$114</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$114</definedName>
+    <definedName name="A2599999R">Data1!$B$1:$B$10,Data1!$B$11:$B$124</definedName>
+    <definedName name="A2599999R_Data">Data1!$B$11:$B$124</definedName>
+    <definedName name="A2599999R_Latest">Data1!$B$124</definedName>
+    <definedName name="A2600000C">Data1!$K$1:$K$10,Data1!$K$11:$K$124</definedName>
+    <definedName name="A2600000C_Data">Data1!$K$11:$K$124</definedName>
+    <definedName name="A2600000C_Latest">Data1!$K$124</definedName>
+    <definedName name="A2600001F">Data1!$T$1:$T$10,Data1!$T$11:$T$124</definedName>
+    <definedName name="A2600001F_Data">Data1!$T$11:$T$124</definedName>
+    <definedName name="A2600001F_Latest">Data1!$T$124</definedName>
+    <definedName name="A2601329C">Data1!$D$1:$D$10,Data1!$D$11:$D$124</definedName>
+    <definedName name="A2601329C_Data">Data1!$D$11:$D$124</definedName>
+    <definedName name="A2601329C_Latest">Data1!$D$124</definedName>
+    <definedName name="A2601330L">Data1!$M$1:$M$10,Data1!$M$11:$M$124</definedName>
+    <definedName name="A2601330L_Data">Data1!$M$11:$M$124</definedName>
+    <definedName name="A2601330L_Latest">Data1!$M$124</definedName>
+    <definedName name="A2601331R">Data1!$V$1:$V$10,Data1!$V$11:$V$124</definedName>
+    <definedName name="A2601331R_Data">Data1!$V$11:$V$124</definedName>
+    <definedName name="A2601331R_Latest">Data1!$V$124</definedName>
+    <definedName name="A2602659L">Data1!$G$1:$G$10,Data1!$G$11:$G$124</definedName>
+    <definedName name="A2602659L_Data">Data1!$G$11:$G$124</definedName>
+    <definedName name="A2602659L_Latest">Data1!$G$124</definedName>
+    <definedName name="A2602660W">Data1!$P$1:$P$10,Data1!$P$11:$P$124</definedName>
+    <definedName name="A2602660W_Data">Data1!$P$11:$P$124</definedName>
+    <definedName name="A2602660W_Latest">Data1!$P$124</definedName>
+    <definedName name="A2602661X">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$124</definedName>
+    <definedName name="A2602661X_Data">Data1!$Y$11:$Y$124</definedName>
+    <definedName name="A2602661X_Latest">Data1!$Y$124</definedName>
+    <definedName name="A2603989W">Data1!$J$1:$J$10,Data1!$J$11:$J$124</definedName>
+    <definedName name="A2603989W_Data">Data1!$J$11:$J$124</definedName>
+    <definedName name="A2603989W_Latest">Data1!$J$124</definedName>
+    <definedName name="A2603990F">Data1!$S$1:$S$10,Data1!$S$11:$S$124</definedName>
+    <definedName name="A2603990F_Data">Data1!$S$11:$S$124</definedName>
+    <definedName name="A2603990F_Latest">Data1!$S$124</definedName>
+    <definedName name="A2603991J">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$124</definedName>
+    <definedName name="A2603991J_Data">Data1!$AB$11:$AB$124</definedName>
+    <definedName name="A2603991J_Latest">Data1!$AB$124</definedName>
+    <definedName name="A2605319W">Data1!$I$1:$I$10,Data1!$I$11:$I$124</definedName>
+    <definedName name="A2605319W_Data">Data1!$I$11:$I$124</definedName>
+    <definedName name="A2605319W_Latest">Data1!$I$124</definedName>
+    <definedName name="A2605320F">Data1!$R$1:$R$10,Data1!$R$11:$R$124</definedName>
+    <definedName name="A2605320F_Data">Data1!$R$11:$R$124</definedName>
+    <definedName name="A2605320F_Latest">Data1!$R$124</definedName>
+    <definedName name="A2605321J">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$124</definedName>
+    <definedName name="A2605321J_Data">Data1!$AA$11:$AA$124</definedName>
+    <definedName name="A2605321J_Latest">Data1!$AA$124</definedName>
+    <definedName name="A2606649F">Data1!$H$1:$H$10,Data1!$H$11:$H$124</definedName>
+    <definedName name="A2606649F_Data">Data1!$H$11:$H$124</definedName>
+    <definedName name="A2606649F_Latest">Data1!$H$124</definedName>
+    <definedName name="A2606650R">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A2606650R_Data">Data1!$Q$11:$Q$124</definedName>
+    <definedName name="A2606650R_Latest">Data1!$Q$124</definedName>
+    <definedName name="A2606651T">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$124</definedName>
+    <definedName name="A2606651T_Data">Data1!$Z$11:$Z$124</definedName>
+    <definedName name="A2606651T_Latest">Data1!$Z$124</definedName>
+    <definedName name="A2607979R">Data1!$F$1:$F$10,Data1!$F$11:$F$124</definedName>
+    <definedName name="A2607979R_Data">Data1!$F$11:$F$124</definedName>
+    <definedName name="A2607979R_Latest">Data1!$F$124</definedName>
+    <definedName name="A2607980X">Data1!$O$1:$O$10,Data1!$O$11:$O$124</definedName>
+    <definedName name="A2607980X_Data">Data1!$O$11:$O$124</definedName>
+    <definedName name="A2607980X_Latest">Data1!$O$124</definedName>
+    <definedName name="A2607981A">Data1!$X$1:$X$10,Data1!$X$11:$X$124</definedName>
+    <definedName name="A2607981A_Data">Data1!$X$11:$X$124</definedName>
+    <definedName name="A2607981A_Latest">Data1!$X$124</definedName>
+    <definedName name="A2609309R">Data1!$C$1:$C$10,Data1!$C$11:$C$124</definedName>
+    <definedName name="A2609309R_Data">Data1!$C$11:$C$124</definedName>
+    <definedName name="A2609309R_Latest">Data1!$C$124</definedName>
+    <definedName name="A2609310X">Data1!$L$1:$L$10,Data1!$L$11:$L$124</definedName>
+    <definedName name="A2609310X_Data">Data1!$L$11:$L$124</definedName>
+    <definedName name="A2609310X_Latest">Data1!$L$124</definedName>
+    <definedName name="A2609311A">Data1!$U$1:$U$10,Data1!$U$11:$U$124</definedName>
+    <definedName name="A2609311A_Data">Data1!$U$11:$U$124</definedName>
+    <definedName name="A2609311A_Latest">Data1!$U$124</definedName>
+    <definedName name="A2610639C">Data1!$E$1:$E$10,Data1!$E$11:$E$124</definedName>
+    <definedName name="A2610639C_Data">Data1!$E$11:$E$124</definedName>
+    <definedName name="A2610639C_Latest">Data1!$E$124</definedName>
+    <definedName name="A2610640L">Data1!$N$1:$N$10,Data1!$N$11:$N$124</definedName>
+    <definedName name="A2610640L_Data">Data1!$N$11:$N$124</definedName>
+    <definedName name="A2610640L_Latest">Data1!$N$124</definedName>
+    <definedName name="A2610641R">Data1!$W$1:$W$10,Data1!$W$11:$W$124</definedName>
+    <definedName name="A2610641R_Data">Data1!$W$11:$W$124</definedName>
+    <definedName name="A2610641R_Latest">Data1!$W$124</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$124</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$124</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1682,7 +1682,7 @@
     <t>Freq.</t>
   </si>
   <si>
-    <t>© Commonwealth of Australia  2023</t>
+    <t>© Commonwealth of Australia  2026</t>
   </si>
 </sst>
 </file>
@@ -2363,10 +2363,10 @@
         <v>35674</v>
       </c>
       <c r="G12" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H12" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>36</v>
@@ -2395,10 +2395,10 @@
         <v>35674</v>
       </c>
       <c r="G13" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H13" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>36</v>
@@ -2427,10 +2427,10 @@
         <v>35674</v>
       </c>
       <c r="G14" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H14" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>36</v>
@@ -2459,10 +2459,10 @@
         <v>35674</v>
       </c>
       <c r="G15" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H15" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>36</v>
@@ -2491,10 +2491,10 @@
         <v>35674</v>
       </c>
       <c r="G16" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H16" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>36</v>
@@ -2523,10 +2523,10 @@
         <v>35674</v>
       </c>
       <c r="G17" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H17" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>36</v>
@@ -2555,10 +2555,10 @@
         <v>35674</v>
       </c>
       <c r="G18" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H18" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>36</v>
@@ -2587,10 +2587,10 @@
         <v>35674</v>
       </c>
       <c r="G19" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H19" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>36</v>
@@ -2619,10 +2619,10 @@
         <v>35674</v>
       </c>
       <c r="G20" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H20" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I20" s="10" t="s">
         <v>36</v>
@@ -2651,10 +2651,10 @@
         <v>35674</v>
       </c>
       <c r="G21" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H21" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>49</v>
@@ -2683,10 +2683,10 @@
         <v>35674</v>
       </c>
       <c r="G22" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H22" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I22" s="10" t="s">
         <v>49</v>
@@ -2715,10 +2715,10 @@
         <v>35674</v>
       </c>
       <c r="G23" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H23" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>49</v>
@@ -2747,10 +2747,10 @@
         <v>35674</v>
       </c>
       <c r="G24" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H24" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I24" s="10" t="s">
         <v>49</v>
@@ -2779,10 +2779,10 @@
         <v>35674</v>
       </c>
       <c r="G25" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H25" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>49</v>
@@ -2811,10 +2811,10 @@
         <v>35674</v>
       </c>
       <c r="G26" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H26" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>49</v>
@@ -2843,10 +2843,10 @@
         <v>35674</v>
       </c>
       <c r="G27" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H27" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>49</v>
@@ -2875,10 +2875,10 @@
         <v>35674</v>
       </c>
       <c r="G28" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H28" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>49</v>
@@ -2907,10 +2907,10 @@
         <v>35674</v>
       </c>
       <c r="G29" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H29" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>49</v>
@@ -2939,10 +2939,10 @@
         <v>35674</v>
       </c>
       <c r="G30" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H30" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>49</v>
@@ -2971,10 +2971,10 @@
         <v>35674</v>
       </c>
       <c r="G31" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H31" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>49</v>
@@ -3003,10 +3003,10 @@
         <v>35674</v>
       </c>
       <c r="G32" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H32" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I32" s="10" t="s">
         <v>49</v>
@@ -3035,10 +3035,10 @@
         <v>35674</v>
       </c>
       <c r="G33" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H33" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I33" s="10" t="s">
         <v>49</v>
@@ -3067,10 +3067,10 @@
         <v>35674</v>
       </c>
       <c r="G34" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H34" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>49</v>
@@ -3099,10 +3099,10 @@
         <v>35674</v>
       </c>
       <c r="G35" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H35" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>49</v>
@@ -3131,10 +3131,10 @@
         <v>35674</v>
       </c>
       <c r="G36" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H36" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>49</v>
@@ -3163,10 +3163,10 @@
         <v>35674</v>
       </c>
       <c r="G37" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H37" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>49</v>
@@ -3195,10 +3195,10 @@
         <v>35674</v>
       </c>
       <c r="G38" s="9">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H38" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>49</v>
@@ -3260,7 +3260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB114"/>
+  <dimension ref="A1:AB124"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -3870,85 +3870,85 @@
         <v>33</v>
       </c>
       <c r="B8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="C8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="D8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="E8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="F8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="G8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="H8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="I8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="J8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="K8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="L8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="M8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="N8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="O8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="P8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Q8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="R8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="S8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="T8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="U8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="V8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="W8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="X8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Y8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="Z8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AA8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
       <c r="AB8" s="6">
-        <v>45078</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -3956,85 +3956,85 @@
         <v>34</v>
       </c>
       <c r="B9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="M9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="O9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="P9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Q9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="R9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="S9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="T9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="U9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="V9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="W9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="X9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Y9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Z9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AA9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="AB9" s="1">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -12975,6 +12975,866 @@
       </c>
       <c r="AB114" s="8">
         <v>3.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A115" s="9">
+        <v>45170</v>
+      </c>
+      <c r="B115" s="8">
+        <v>146.80000000000001</v>
+      </c>
+      <c r="C115" s="8">
+        <v>151.69999999999999</v>
+      </c>
+      <c r="D115" s="8">
+        <v>153</v>
+      </c>
+      <c r="E115" s="8">
+        <v>144.4</v>
+      </c>
+      <c r="F115" s="8">
+        <v>148.5</v>
+      </c>
+      <c r="G115" s="8">
+        <v>147.5</v>
+      </c>
+      <c r="H115" s="8">
+        <v>148.5</v>
+      </c>
+      <c r="I115" s="8">
+        <v>141.69999999999999</v>
+      </c>
+      <c r="J115" s="8">
+        <v>149.1</v>
+      </c>
+      <c r="K115" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="L115" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="M115" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="N115" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="O115" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P115" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q115" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="R115" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="S115" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T115" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="U115" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="V115" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W115" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="X115" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="Y115" s="8">
+        <v>4</v>
+      </c>
+      <c r="Z115" s="8">
+        <v>3</v>
+      </c>
+      <c r="AA115" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="AB115" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A116" s="9">
+        <v>45261</v>
+      </c>
+      <c r="B116" s="8">
+        <v>151.30000000000001</v>
+      </c>
+      <c r="C116" s="8">
+        <v>152.6</v>
+      </c>
+      <c r="D116" s="8">
+        <v>154.9</v>
+      </c>
+      <c r="E116" s="8">
+        <v>145.5</v>
+      </c>
+      <c r="F116" s="8">
+        <v>150</v>
+      </c>
+      <c r="G116" s="8">
+        <v>147.9</v>
+      </c>
+      <c r="H116" s="8">
+        <v>150.1</v>
+      </c>
+      <c r="I116" s="8">
+        <v>142.80000000000001</v>
+      </c>
+      <c r="J116" s="8">
+        <v>151.4</v>
+      </c>
+      <c r="K116" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="L116" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="M116" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="N116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="O116" s="8">
+        <v>1</v>
+      </c>
+      <c r="P116" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="Q116" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R116" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="S116" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="T116" s="8">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="U116" s="8">
+        <v>2.8</v>
+      </c>
+      <c r="V116" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="W116" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X116" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="Y116" s="8">
+        <v>4</v>
+      </c>
+      <c r="Z116" s="8">
+        <v>4</v>
+      </c>
+      <c r="AA116" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="AB116" s="8">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A117" s="9">
+        <v>45352</v>
+      </c>
+      <c r="B117" s="8">
+        <v>151.80000000000001</v>
+      </c>
+      <c r="C117" s="8">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="D117" s="8">
+        <v>156.1</v>
+      </c>
+      <c r="E117" s="8">
+        <v>146.4</v>
+      </c>
+      <c r="F117" s="8">
+        <v>150.5</v>
+      </c>
+      <c r="G117" s="8">
+        <v>152.5</v>
+      </c>
+      <c r="H117" s="8">
+        <v>150.5</v>
+      </c>
+      <c r="I117" s="8">
+        <v>143.5</v>
+      </c>
+      <c r="J117" s="8">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="K117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="L117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M117" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="N117" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="P117" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="Q117" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="R117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S117" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T117" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="U117" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="V117" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="W117" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="X117" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="Y117" s="8">
+        <v>5</v>
+      </c>
+      <c r="Z117" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="AA117" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="AB117" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A118" s="9">
+        <v>45444</v>
+      </c>
+      <c r="B118" s="8">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="C118" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="D118" s="8">
+        <v>157.4</v>
+      </c>
+      <c r="E118" s="8">
+        <v>148.9</v>
+      </c>
+      <c r="F118" s="8">
+        <v>150.9</v>
+      </c>
+      <c r="G118" s="8">
+        <v>153.6</v>
+      </c>
+      <c r="H118" s="8">
+        <v>150.6</v>
+      </c>
+      <c r="I118" s="8">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="J118" s="8">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="K118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="L118" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="M118" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="N118" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="O118" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="P118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="Q118" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="R118" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="S118" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="T118" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="U118" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="V118" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="W118" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="X118" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="Y118" s="8">
+        <v>5.2</v>
+      </c>
+      <c r="Z118" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="AA118" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="AB118" s="8">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A119" s="9">
+        <v>45536</v>
+      </c>
+      <c r="B119" s="8">
+        <v>153.30000000000001</v>
+      </c>
+      <c r="C119" s="8">
+        <v>155.4</v>
+      </c>
+      <c r="D119" s="8">
+        <v>159.9</v>
+      </c>
+      <c r="E119" s="8">
+        <v>149.5</v>
+      </c>
+      <c r="F119" s="8">
+        <v>151.69999999999999</v>
+      </c>
+      <c r="G119" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="H119" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="I119" s="8">
+        <v>148</v>
+      </c>
+      <c r="J119" s="8">
+        <v>154.6</v>
+      </c>
+      <c r="K119" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="L119" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="M119" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="N119" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="O119" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P119" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="R119" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S119" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="T119" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U119" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="V119" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="W119" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="X119" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Y119" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="Z119" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="AA119" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AB119" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A120" s="9">
+        <v>45627</v>
+      </c>
+      <c r="B120" s="8">
+        <v>154</v>
+      </c>
+      <c r="C120" s="8">
+        <v>157</v>
+      </c>
+      <c r="D120" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="E120" s="8">
+        <v>150.19999999999999</v>
+      </c>
+      <c r="F120" s="8">
+        <v>153.1</v>
+      </c>
+      <c r="G120" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="H120" s="8">
+        <v>154.80000000000001</v>
+      </c>
+      <c r="I120" s="8">
+        <v>148.6</v>
+      </c>
+      <c r="J120" s="8">
+        <v>155.80000000000001</v>
+      </c>
+      <c r="K120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="8">
+        <v>1</v>
+      </c>
+      <c r="M120" s="8">
+        <v>1</v>
+      </c>
+      <c r="N120" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O120" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="P120" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="R120" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="S120" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="T120" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="U120" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="V120" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="W120" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="X120" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="Y120" s="8">
+        <v>4.7</v>
+      </c>
+      <c r="Z120" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="AA120" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AB120" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A121" s="9">
+        <v>45717</v>
+      </c>
+      <c r="B121" s="8">
+        <v>157.1</v>
+      </c>
+      <c r="C121" s="8">
+        <v>157.9</v>
+      </c>
+      <c r="D121" s="8">
+        <v>162.19999999999999</v>
+      </c>
+      <c r="E121" s="8">
+        <v>151.19999999999999</v>
+      </c>
+      <c r="F121" s="8">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="G121" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="H121" s="8">
+        <v>155.5</v>
+      </c>
+      <c r="I121" s="8">
+        <v>150.4</v>
+      </c>
+      <c r="J121" s="8">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="K121" s="8">
+        <v>2</v>
+      </c>
+      <c r="L121" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="M121" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="N121" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="O121" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="P121" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="Q121" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R121" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="S121" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="T121" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="U121" s="8">
+        <v>3</v>
+      </c>
+      <c r="V121" s="8">
+        <v>3.9</v>
+      </c>
+      <c r="W121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="X121" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="Y121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="Z121" s="8">
+        <v>3.3</v>
+      </c>
+      <c r="AA121" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="AB121" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A122" s="9">
+        <v>45809</v>
+      </c>
+      <c r="B122" s="8">
+        <v>157.6</v>
+      </c>
+      <c r="C122" s="8">
+        <v>159.19999999999999</v>
+      </c>
+      <c r="D122" s="8">
+        <v>163.1</v>
+      </c>
+      <c r="E122" s="8">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="F122" s="8">
+        <v>159</v>
+      </c>
+      <c r="G122" s="8">
+        <v>158.9</v>
+      </c>
+      <c r="H122" s="8">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="I122" s="8">
+        <v>153.5</v>
+      </c>
+      <c r="J122" s="8">
+        <v>158.9</v>
+      </c>
+      <c r="K122" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="L122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="M122" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="N122" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O122" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="Q122" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="R122" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="S122" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="T122" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="U122" s="8">
+        <v>3.2</v>
+      </c>
+      <c r="V122" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="W122" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="X122" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="Y122" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="Z122" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="AA122" s="8">
+        <v>4.3</v>
+      </c>
+      <c r="AB122" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A123" s="9">
+        <v>45901</v>
+      </c>
+      <c r="B123" s="8">
+        <v>160</v>
+      </c>
+      <c r="C123" s="8">
+        <v>160.9</v>
+      </c>
+      <c r="D123" s="8">
+        <v>163.69999999999999</v>
+      </c>
+      <c r="E123" s="8">
+        <v>153.6</v>
+      </c>
+      <c r="F123" s="8">
+        <v>162</v>
+      </c>
+      <c r="G123" s="8">
+        <v>159.9</v>
+      </c>
+      <c r="H123" s="8">
+        <v>156.30000000000001</v>
+      </c>
+      <c r="I123" s="8">
+        <v>154</v>
+      </c>
+      <c r="J123" s="8">
+        <v>160.5</v>
+      </c>
+      <c r="K123" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="L123" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M123" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="N123" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O123" s="8">
+        <v>1.9</v>
+      </c>
+      <c r="P123" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="Q123" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="R123" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="S123" s="8">
+        <v>1</v>
+      </c>
+      <c r="T123" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="U123" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="V123" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="W123" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="X123" s="8">
+        <v>6.8</v>
+      </c>
+      <c r="Y123" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="Z123" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AA123" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AB123" s="8">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A124" s="9">
+        <v>45992</v>
+      </c>
+      <c r="B124" s="8">
+        <v>162.69999999999999</v>
+      </c>
+      <c r="C124" s="8">
+        <v>161.5</v>
+      </c>
+      <c r="D124" s="8">
+        <v>164.9</v>
+      </c>
+      <c r="E124" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="F124" s="8">
+        <v>163.80000000000001</v>
+      </c>
+      <c r="G124" s="8">
+        <v>160.5</v>
+      </c>
+      <c r="H124" s="8">
+        <v>156.9</v>
+      </c>
+      <c r="I124" s="8">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="J124" s="8">
+        <v>161.9</v>
+      </c>
+      <c r="K124" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="L124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="M124" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="N124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="O124" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="Q124" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="R124" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="S124" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="T124" s="8">
+        <v>5.6</v>
+      </c>
+      <c r="U124" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="V124" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="W124" s="8">
+        <v>2.7</v>
+      </c>
+      <c r="X124" s="8">
+        <v>7</v>
+      </c>
+      <c r="Y124" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="Z124" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="AA124" s="8">
+        <v>3.8</v>
+      </c>
+      <c r="AB124" s="8">
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
